--- a/survey_templates/047_music_streaming_app_interface_feedback_survey--survey_templates.xlsx
+++ b/survey_templates/047_music_streaming_app_interface_feedback_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -755,7 +755,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Question 3 Other</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -870,7 +870,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Category 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -893,7 +893,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Subcategory</t>
+          <t>Subcategory 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -939,7 +939,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Other (please specify)</t>
+          <t>Question 4 Other</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -964,8 +964,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -993,12 +993,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'main_menu'}</t>
+          <t>main_menu</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Main Menu'}</t>
+          <t>Main Menu</t>
         </is>
       </c>
     </row>
@@ -1010,12 +1010,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'search'}</t>
+          <t>search</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Search'}</t>
+          <t>Search</t>
         </is>
       </c>
     </row>
@@ -1027,12 +1027,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'profile'}</t>
+          <t>profile</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Profile'}</t>
+          <t>Profile</t>
         </is>
       </c>
     </row>
@@ -1044,12 +1044,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'easy_to_use'}</t>
+          <t>easy_to_use</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Easy to use'}</t>
+          <t>Easy to use</t>
         </is>
       </c>
     </row>
@@ -1061,12 +1061,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'confusing'}</t>
+          <t>confusing</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Confusing'}</t>
+          <t>Confusing</t>
         </is>
       </c>
     </row>
@@ -1078,12 +1078,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'unnecessary_feature'}</t>
+          <t>unnecessary_feature</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Unnecessary feature'}</t>
+          <t>Unnecessary feature</t>
         </is>
       </c>
     </row>
@@ -1095,12 +1095,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'very_good'}</t>
+          <t>very_good</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Very good'}</t>
+          <t>Very good</t>
         </is>
       </c>
     </row>
@@ -1112,12 +1112,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'not_good_at_all'}</t>
+          <t>not_good_at_all</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Not good at all'}</t>
+          <t>Not good at all</t>
         </is>
       </c>
     </row>
@@ -1129,12 +1129,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat'}</t>
+          <t>somewhat</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat'}</t>
+          <t>Somewhat</t>
         </is>
       </c>
     </row>
@@ -1146,12 +1146,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'neither'}</t>
+          <t>neither</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Neither'}</t>
+          <t>Neither</t>
         </is>
       </c>
     </row>
@@ -1163,12 +1163,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'very_good'}</t>
+          <t>very_good</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Very good'}</t>
+          <t>Very good</t>
         </is>
       </c>
     </row>
@@ -1180,12 +1180,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'not_good_at_all'}</t>
+          <t>not_good_at_all</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Not good at all'}</t>
+          <t>Not good at all</t>
         </is>
       </c>
     </row>
@@ -1197,12 +1197,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat'}</t>
+          <t>somewhat</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat'}</t>
+          <t>Somewhat</t>
         </is>
       </c>
     </row>
@@ -1214,12 +1214,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'neither'}</t>
+          <t>neither</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Neither'}</t>
+          <t>Neither</t>
         </is>
       </c>
     </row>
